--- a/inputs/es/LiST countries/MEX_databook.xlsx
+++ b/inputs/es/LiST countries/MEX_databook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5121E57-4368-4373-AC98-A4F0CB6D6194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA97069-E0F1-47F8-BE66-685505954FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Distribución estado nutricional" sheetId="4" r:id="rId4"/>
     <sheet name="Distribución de lactancia" sheetId="5" r:id="rId5"/>
     <sheet name="Tendencias temporales" sheetId="6" r:id="rId6"/>
-    <sheet name="Variables económicas   " sheetId="7" r:id="rId7"/>
+    <sheet name="Variables económicas" sheetId="7" r:id="rId7"/>
     <sheet name="Paquetes de IYCF" sheetId="8" r:id="rId8"/>
     <sheet name="Tratamiento de la MAS" sheetId="9" r:id="rId9"/>
     <sheet name="Costo y cobertura del programa" sheetId="10" r:id="rId10"/>
@@ -20814,6 +20814,35 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="BsgSmPKG0UK6k6Hb2Zr7YG4R19ko82pniBaWlLDy+tBV7jZ5+2PUE8GgQdhaxOr6fwvTZaA/f/zitKbOG2nbuQ==" saltValue="prUnPSuL08Def2RKOezIXA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B142:B144"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B111:B113"/>
@@ -20830,35 +20859,6 @@
     <mergeCell ref="B98:B100"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B89:B91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -41619,15 +41619,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
@@ -41635,6 +41626,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41822,19 +41822,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/inputs/es/LiST countries/MEX_databook.xlsx
+++ b/inputs/es/LiST countries/MEX_databook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\LiST countries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modelling projects\Nutrition\inputs\es\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB42A4A5-F11E-4131-B8FD-8666DA4EC29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8667AA11-9165-40D0-B3B3-A8AC3793F9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -2690,6 +2690,74 @@
         </r>
       </text>
     </comment>
+    <comment ref="L37" authorId="1" shapeId="0" xr:uid="{B53E2CCE-449F-4B13-937B-3F8B887F6752}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M37" authorId="1" shapeId="0" xr:uid="{1148A5A1-251A-4064-B40F-0C8735779040}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N37" authorId="1" shapeId="0" xr:uid="{15C867EE-F338-4C14-9C7D-F0E3CF1EF5FB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O37" authorId="1" shapeId="0" xr:uid="{8E4E4ECE-5F5C-4FD8-8945-6257CBFF139B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
@@ -3928,7 +3996,7 @@
     <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{6BB5D3EA-EB2C-4557-A77A-BC3B31DE5A74}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{E6EBA730-3C9A-42F5-8372-C12E3D2BCF23}">
       <text>
         <r>
           <rPr>
@@ -3942,7 +4010,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{8276B184-5391-46AC-9017-CD45ED68E7E2}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{AF9DB01E-B712-4A66-A517-1C057B372D40}">
       <text>
         <r>
           <rPr>
@@ -3956,7 +4024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{70662288-9B2B-4D49-A059-B389A408D887}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{207C9149-2C56-40E5-890F-83153B938A2F}">
       <text>
         <r>
           <rPr>
@@ -3970,7 +4038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{5F99FF59-4E44-4847-82EE-D42B7418AA00}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{39C4CB92-7EE0-4046-B67E-41191387FFA0}">
       <text>
         <r>
           <rPr>
@@ -3984,7 +4052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{F6C9465E-FBDE-45D1-8394-CD6F9C9C2529}">
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{E377B1E7-A333-4A74-97C3-029328512C07}">
       <text>
         <r>
           <rPr>
@@ -3998,7 +4066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{8724D448-9507-4D14-BCA7-F21B3CAF1BD6}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{200C4BAB-9EE2-447E-A6DD-80717CFE4AC8}">
       <text>
         <r>
           <rPr>
@@ -4012,7 +4080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{1D086CE7-3639-4C5A-8FD3-DB935503731C}">
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{9FC7E5D2-2D8B-4961-9B75-5691D4A68B0C}">
       <text>
         <r>
           <rPr>
@@ -4026,7 +4094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{1EDBAC82-3035-4B47-8DB4-6C9605D373FF}">
+    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{D951D76C-28E5-48CE-899C-D128152950FC}">
       <text>
         <r>
           <rPr>
@@ -4040,7 +4108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{F889FFDD-F5D3-428F-97C9-3FA317F4DEEC}">
+    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{E9DCEC9B-12F6-42CF-8CD9-B1C5DD42DE71}">
       <text>
         <r>
           <rPr>
@@ -4054,7 +4122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{178C61B9-10CF-475E-AE2A-1148BD159501}">
+    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{9FD33C3F-D78F-4E9D-A67C-9D39AC73491A}">
       <text>
         <r>
           <rPr>
@@ -4068,7 +4136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{D1ADD6AA-00B3-496F-889D-6AD9E8EC7261}">
+    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{3400288E-DF03-41FF-B1F2-3EB20AA1B927}">
       <text>
         <r>
           <rPr>
@@ -4082,7 +4150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{D8A7821F-2C8B-4B9F-B2CF-783B6F1D6ACB}">
+    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{9C325214-076C-49F4-9A1C-FDD39C7EF1F6}">
       <text>
         <r>
           <rPr>
@@ -4096,7 +4164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{30A88894-D578-48EA-8642-A1FBFF69A3C1}">
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{9B6733C4-FA93-4154-8674-5B85D19B6115}">
       <text>
         <r>
           <rPr>
@@ -4110,7 +4178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{1FC0B5F8-9FC2-4095-AEC3-321F62EB13E4}">
+    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{0607EB3C-B9C7-4D01-AE82-3B20B34591B6}">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{037243D6-BCDE-4F6B-AFCC-3F94A0DD5E02}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{26DD0551-BD1F-450A-8953-951E786BA725}">
       <text>
         <r>
           <rPr>
@@ -4138,7 +4206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{DE335ADC-5DD3-496C-A5AC-AAE47036457E}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{07B0F43C-E3A4-41A5-9220-14111D4DE5D5}">
       <text>
         <r>
           <rPr>
@@ -4152,7 +4220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{2912EBE3-D556-42B6-96D5-24EC21E6156C}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{BF774CA2-E4B3-46E6-A04D-901C8156EE77}">
       <text>
         <r>
           <rPr>
@@ -4166,7 +4234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{4CB9182B-79CD-4596-8295-56AF4E3846AB}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{DDFF231A-B050-4E30-B877-4FB8473D71B0}">
       <text>
         <r>
           <rPr>
@@ -4180,7 +4248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{80F6289A-949B-4FAE-AC85-22980BCEA4F4}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{0214BC76-CC8A-414C-8D7A-C51B3E742D6B}">
       <text>
         <r>
           <rPr>
@@ -4204,7 +4272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{96FCBC9B-E5EC-46B8-8DF3-3E8D35EE350D}">
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{408E5496-8B3D-4F1E-BD84-9A9255C25832}">
       <text>
         <r>
           <rPr>
@@ -4218,7 +4286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{93171B53-CE10-41E2-9E96-E27147D4D778}">
+    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{DF0EEE5A-AAEC-4832-9B3D-B069B0FD3D24}">
       <text>
         <r>
           <rPr>
@@ -4232,7 +4300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{5FE03E37-E69F-43F4-B94E-7BBC3063A87D}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{2A9C86D6-9952-4010-8EF5-ED482E1554FE}">
       <text>
         <r>
           <rPr>
@@ -4247,7 +4315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{626B60BA-B78A-4BE5-ACC0-D15C014DDDE7}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{5A70274A-2FB2-4238-A065-120459AD1B15}">
       <text>
         <r>
           <rPr>
@@ -4262,7 +4330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{A6D7FDB2-70C1-4A3F-AE05-E1F583DAC911}">
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{385F9BE4-A3AC-4198-BAC3-722E7A520402}">
       <text>
         <r>
           <rPr>
@@ -4277,7 +4345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{73FE6ADA-DBBD-4E18-9E0A-7E9F1B65F4FF}">
+    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{1E0B57C8-7A0A-48E3-A3E8-1E19A7175498}">
       <text>
         <r>
           <rPr>
@@ -4292,7 +4360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{36DC02C6-7D52-483D-9E4D-A62E1832D1E9}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{2AC9637A-4534-4154-9BD7-3AE7DD8CD9DD}">
       <text>
         <r>
           <rPr>
@@ -4307,7 +4375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{3A418ECB-CB98-4DAE-914F-181BDF7ED565}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{01A3CEF9-0D30-4FDB-AF26-2DC31C7D29F6}">
       <text>
         <r>
           <rPr>
@@ -4322,7 +4390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{F54E6507-D7CB-4F8D-8BA0-8C678AC88484}">
+    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{E3448607-813B-4893-BFAF-1777B6724FBF}">
       <text>
         <r>
           <rPr>
@@ -4337,7 +4405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{51D136EC-624C-44D3-B5B3-53EE7A4C79F4}">
+    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{CB33591A-EF28-41CE-A9F1-ECF332B1A04F}">
       <text>
         <r>
           <rPr>
@@ -4352,7 +4420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{0358037B-23C7-469B-B136-BD3C312D371A}">
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{652EDCEE-9F4F-4011-BE3F-87A81AEAB68F}">
       <text>
         <r>
           <rPr>
@@ -4366,7 +4434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{83DD7CE2-EBA6-4C72-A5A2-1E7961104F35}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{F2E7DF39-BD3C-4774-9BD5-66837E9E22BF}">
       <text>
         <r>
           <rPr>
@@ -4380,7 +4448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{D00C0728-6CE5-4232-9E9D-03298AA7E83F}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{84346A43-22E1-4209-86B7-5484553C9A3C}">
       <text>
         <r>
           <rPr>
@@ -4394,7 +4462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{DE005C0A-2F8A-418C-851E-64B2B8CFE1FA}">
+    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{6AA73D8B-E906-4C63-9A89-433F265EDADB}">
       <text>
         <r>
           <rPr>
@@ -4408,7 +4476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{E55324F7-370C-4385-ADBA-E8B0EBEB4BEC}">
+    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{D0DB495D-46B4-4957-B9C2-D1B5214046C5}">
       <text>
         <r>
           <rPr>
@@ -4422,7 +4490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{F53439F8-F18B-45A1-B265-14A4B9BFCA4E}">
+    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{E8F934AE-F36A-4978-A2B4-5231B12CD33F}">
       <text>
         <r>
           <rPr>
@@ -4436,7 +4504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{D3552897-BBD5-4175-B68A-A3F1E4A6E75C}">
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{53D9CECE-9FA0-4330-B76A-C6EEC6C1D659}">
       <text>
         <r>
           <rPr>
@@ -4450,7 +4518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{CC47941B-D047-44AD-8609-225A3A1207CF}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{9DC905D6-8DE5-4FE7-BE6F-D3E934A75201}">
       <text>
         <r>
           <rPr>
@@ -4464,7 +4532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{0CBE3706-3924-4509-A583-88069D4C218C}">
+    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{ACC4B3F7-E558-402F-BE57-0C3DDC8060F5}">
       <text>
         <r>
           <rPr>
@@ -4478,7 +4546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{A5F6F3D3-D70F-4D04-A795-6D6BF5E34983}">
+    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{955FA18E-86F7-422C-8CA5-A38FE4881347}">
       <text>
         <r>
           <rPr>
@@ -4492,7 +4560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{DD598447-A738-4E83-BE84-12132D14A7E3}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{33441C3A-E101-49E5-A4DB-504F222DBABB}">
       <text>
         <r>
           <rPr>
@@ -4507,7 +4575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{AAC1265A-FBA5-4B61-B6FD-C1ADAB02C015}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{9A6BDF27-568B-45B9-BE8D-362C80D286A5}">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{CB5BEA38-52BE-4279-8999-876D134092DA}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{08FA6FC1-5E34-45F1-9F8B-4E7BAEF15D4E}">
       <text>
         <r>
           <rPr>
@@ -4537,7 +4605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{EEC82E46-7238-472F-8156-89C286EC0CC5}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{E9730E75-4547-4DE1-A9F2-FCA6D5B09778}">
       <text>
         <r>
           <rPr>
@@ -4552,7 +4620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{9AD99541-38BF-452C-BBDF-30A63672B134}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{38945CFE-2923-4A7C-9E0E-820E103F12F0}">
       <text>
         <r>
           <rPr>
@@ -4567,7 +4635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{9F2485E2-4FB1-40DF-95BC-EF307614F383}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{F76610CF-AE5A-4A2B-BD5A-C60057991BBE}">
       <text>
         <r>
           <rPr>
@@ -4583,7 +4651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{5A344499-6486-4E45-BC00-E472735A7CB2}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{8EC67AD9-5004-458A-B78A-27343190877D}">
       <text>
         <r>
           <rPr>
@@ -4599,7 +4667,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{031BB5AD-8138-4687-BD78-7EBC20A98663}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{8D6C5816-8BDB-4D07-A205-24F2394A4590}">
       <text>
         <r>
           <rPr>
@@ -4615,7 +4683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{184A5B5A-1F15-44FE-898C-B90309E01D89}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{B76A1BFB-64B6-4C17-9732-138D8EB49340}">
       <text>
         <r>
           <rPr>
@@ -4631,7 +4699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{8ED585B4-389F-460E-8916-C9CBE4D87E3D}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{962C7931-87AA-452E-BF56-06BF5EBED30C}">
       <text>
         <r>
           <rPr>
@@ -4647,7 +4715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{AD24A257-1231-432A-9AC2-49A1BBCFE8E5}">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{25F108DC-6C32-4B96-9492-1B12A3709CE9}">
       <text>
         <r>
           <rPr>
@@ -4662,7 +4730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{A07ED250-D084-453F-8461-66EC0C10E110}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{8B1376CD-B39F-49F6-BC5B-7A2858E0592C}">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{9059BCA8-1FD3-4E64-86A7-3061E1F307E3}">
+    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{048CF327-553B-4B14-8A84-22CC73D47D4A}">
       <text>
         <r>
           <rPr>
@@ -4692,7 +4760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{7052734F-4036-424E-8991-EAD18C6FC7CF}">
+    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{1FFD936D-DA45-475C-9F30-391304B2787A}">
       <text>
         <r>
           <rPr>
@@ -4707,7 +4775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{9211745A-0C8C-4E89-B62F-2D6F1D5B7D01}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{3CED59C7-FFD8-4D8E-9210-1FB3B9F57245}">
       <text>
         <r>
           <rPr>
@@ -4722,7 +4790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{5423B35A-FBAB-43E1-A574-44F7790EAEA1}">
+    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{BFC97A30-BB96-4307-90EA-5BE03611C63A}">
       <text>
         <r>
           <rPr>
@@ -4736,7 +4804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{9923839E-0345-401E-8DBE-0D84F514E4A9}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{51ED88B2-1E5E-47FC-9698-0E5AB645D504}">
       <text>
         <r>
           <rPr>
@@ -4750,7 +4818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{BA7FE3E3-08B4-4F16-B01F-05A523005C56}">
+    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{561CB528-6BAE-4817-8CC0-243735B76FA1}">
       <text>
         <r>
           <rPr>
@@ -4764,7 +4832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{6D26BBC2-8403-47E0-89A8-CCA5B5E2A63F}">
+    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{E496632C-74C0-41C8-9AB4-0B4C87893674}">
       <text>
         <r>
           <rPr>
@@ -4778,7 +4846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{4063B8B9-975B-4060-938A-48F03FAEF419}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{FBF69FC4-CD17-4513-AF48-E695A29BF824}">
       <text>
         <r>
           <rPr>
@@ -4792,7 +4860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{50660BAB-9FCC-42B5-9F93-0DBB8CA89897}">
+    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{900E651E-9020-4856-BB60-BF507FACE1CC}">
       <text>
         <r>
           <rPr>
@@ -4806,7 +4874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{C6A07F78-8D75-479F-926E-474BA841B234}">
+    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{49F9B2F7-6FD6-4FDF-921C-425B5CDD5155}">
       <text>
         <r>
           <rPr>
@@ -4820,7 +4888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{FA86AF70-4991-447A-BCAA-1000A44BF256}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{4AC52846-7242-459E-9C8D-BF78F201C110}">
       <text>
         <r>
           <rPr>
@@ -4834,7 +4902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{FD47D524-CA3E-4654-B95C-882313C71EE4}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{B7E52F08-0E63-474C-A17D-FB71B12C1A4F}">
       <text>
         <r>
           <rPr>
@@ -4848,7 +4916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{350D10EC-94B3-4790-8891-B0A27313C3E5}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{329CDC5B-FBD8-45AA-9D30-2F9915F0B0DB}">
       <text>
         <r>
           <rPr>
@@ -4862,7 +4930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{E54F70F0-DBA3-4F25-90EB-D1DFD3641E6A}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{74D24310-E8B6-4724-B08F-C246A0B86F17}">
       <text>
         <r>
           <rPr>
@@ -4876,7 +4944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{77363AFB-2A43-477F-8EB8-CC2F7E3ECEA0}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{7026E01B-E53C-4032-904B-4C8C6143328A}">
       <text>
         <r>
           <rPr>
@@ -4890,7 +4958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{01109C22-04ED-4FDB-949C-C34810AB2E95}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{56E6B52D-1C74-48A6-AB95-D033A5B5881A}">
       <text>
         <r>
           <rPr>
@@ -4904,7 +4972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{72F3E256-254B-4FFC-9E01-1752BCF475A6}">
+    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{A2996F6D-43C2-499B-8B4D-F7E668692366}">
       <text>
         <r>
           <rPr>
@@ -4918,7 +4986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{E057EF81-59F3-42CB-9D3F-907D93019067}">
+    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{1BA30CAA-FFAB-42ED-B857-7C2DBF6DD53A}">
       <text>
         <r>
           <rPr>
@@ -4932,7 +5000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{DF457454-4973-4207-9E3D-7D50D7830FDE}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{234E5DD0-50F5-435F-A2AD-FDCE2659B300}">
       <text>
         <r>
           <rPr>
@@ -4946,7 +5014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{0A31E4B1-743B-4208-AE2B-4146BBD81A93}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{81B268C8-266C-41E0-8968-7FD59EF44415}">
       <text>
         <r>
           <rPr>
@@ -4960,7 +5028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{BA5122FC-4C8D-49F0-9902-8C88B2457CA4}">
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{D68CDFE1-6866-4AC0-B4D7-B34E1A995637}">
       <text>
         <r>
           <rPr>
@@ -4974,7 +5042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{EB775666-1A82-4D30-A432-4C033A1A7AED}">
+    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{6447B983-C337-44DD-BE06-3BF10916980C}">
       <text>
         <r>
           <rPr>
@@ -4988,7 +5056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{98BB8C6D-B30B-4DB6-8B35-7D8DCE93E79C}">
+    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{42AC3582-1D7E-471B-A6C7-CD7E77F8588B}">
       <text>
         <r>
           <rPr>
@@ -5003,7 +5071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{75544419-0995-4A7F-98E3-CBE19D6471D0}">
+    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{C499C901-0DF0-4641-8493-EE778DE73B96}">
       <text>
         <r>
           <rPr>
@@ -5018,7 +5086,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{866B3636-D1B7-40EE-A9B3-22FD1891C340}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{080FF01F-34D3-44B7-835E-C7CC7A5B457C}">
       <text>
         <r>
           <rPr>
@@ -5033,7 +5101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{3C5743BD-EFCC-4AF2-B330-6FDF8775A9D5}">
+    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{B263C3DB-9806-4F53-B7FE-F5AB30086A04}">
       <text>
         <r>
           <rPr>
@@ -5048,7 +5116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{07C4191C-0E34-4B64-AAF8-A7F551741AB2}">
+    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{FF88E7CE-1D54-4693-9AC1-0680C2879226}">
       <text>
         <r>
           <rPr>
@@ -5063,7 +5131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{419B2D75-98C1-46B5-842D-118FC911FF04}">
+    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{F32BE7CD-2AAA-47AD-914F-4CAAC1FEDD3B}">
       <text>
         <r>
           <rPr>
@@ -5078,7 +5146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{A1CD6A7F-EF69-49BD-84EA-F060EB24114F}">
+    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{BCFCAE2C-B071-4EBD-916E-9CB34A3AE95A}">
       <text>
         <r>
           <rPr>
@@ -5093,7 +5161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{D5825461-688C-438C-8542-BD85D579FDC7}">
+    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{E2890E16-5EE9-49DE-B974-B3ADDC0025FE}">
       <text>
         <r>
           <rPr>
@@ -5108,7 +5176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{AF7C92B2-AC28-43C3-9C19-D68E37FF28FD}">
+    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{FFC68E24-6D1B-4208-B66E-D8A12166F7EF}">
       <text>
         <r>
           <rPr>
@@ -5123,7 +5191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{700142E9-6A7D-415A-8AA2-F2A8B6A75555}">
+    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{AE98D75E-0886-4415-A5FC-355EDA6C4FF5}">
       <text>
         <r>
           <rPr>
@@ -5138,7 +5206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{7D67AB3C-983B-47D0-9AFF-DA097636CBA4}">
+    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{F3FF4EFF-507E-406A-9019-C50AD187D27F}">
       <text>
         <r>
           <rPr>
@@ -5152,7 +5220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{38FC6B21-5384-4027-AE29-F2FF12011A26}">
+    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{DE5B9A2C-A2CF-41B4-A227-60CE716BCCA3}">
       <text>
         <r>
           <rPr>
@@ -5166,7 +5234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{EB3D123B-E86C-4173-B872-21E041277078}">
+    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{34EEDC69-740F-43FD-A983-6FB9711FB123}">
       <text>
         <r>
           <rPr>
@@ -5180,7 +5248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C5BAFDF7-3C0B-454A-B8DD-17A5272728F7}">
+    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C1C7CF2A-6820-4496-B5B3-46A027800BF9}">
       <text>
         <r>
           <rPr>
@@ -5194,7 +5262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{BB84B4E6-6EBF-43F8-A27F-ABACD68A728A}">
+    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{EBC10A23-30BF-4E42-8CA2-8EE10D6CA31A}">
       <text>
         <r>
           <rPr>
@@ -5208,7 +5276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{BFD18A89-7D4A-4FA5-8D9C-46BDFC49F7B4}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{C4570B06-D8B9-4BF0-8899-481D28F107D4}">
       <text>
         <r>
           <rPr>
@@ -5223,7 +5291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{1ABF9016-F3C2-48B1-BD46-AD89F4003AC8}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{E10AAA50-CCAF-4DFB-8CEA-438EA6695142}">
       <text>
         <r>
           <rPr>
@@ -5238,7 +5306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{6A6E8E29-2989-40FF-B168-55803883F0D8}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{0D2DBAA3-0B85-4069-9696-DDECC83557DF}">
       <text>
         <r>
           <rPr>
@@ -5253,7 +5321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{48DA76B4-3665-4A45-819A-BFEEFF70E5D8}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{E6F4F3F2-6816-43AD-9558-8D77B03CE641}">
       <text>
         <r>
           <rPr>
@@ -5268,7 +5336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{B80ED8C6-87BC-498B-8629-005BCCE79F4B}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{994813E0-DC6E-4867-8FA2-13765D152F5E}">
       <text>
         <r>
           <rPr>
@@ -5283,7 +5351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{B5F2ED77-4534-4005-9653-3943813A8B21}">
+    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{6D709644-E2DA-4998-B8D6-CCE8241FA062}">
       <text>
         <r>
           <rPr>
@@ -5299,7 +5367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{76285A74-606B-4904-9089-8C072E19A125}">
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{E0BF8484-6C50-4B90-B5C7-81D81EF18053}">
       <text>
         <r>
           <rPr>
@@ -5315,7 +5383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{63134AD8-900C-4178-BB9D-773F5A2AEB3B}">
+    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{98B23DB2-DC71-4976-B9E0-A2E971751C45}">
       <text>
         <r>
           <rPr>
@@ -5331,7 +5399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{E4550204-DAD5-4F24-9613-4B653BB1BEF9}">
+    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{EED7AE56-914C-4919-99D9-9B4DD94D01A5}">
       <text>
         <r>
           <rPr>
@@ -5347,7 +5415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{8EB04C99-52A7-4C56-9738-8833ED4CF79E}">
+    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{C946989D-0B8C-452F-9FD8-02724BD02182}">
       <text>
         <r>
           <rPr>
@@ -5363,7 +5431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{1E087D6A-9C87-4366-B106-9662D0E9F522}">
+    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{E509D43A-5096-49C2-BA18-0C199C6BF4A8}">
       <text>
         <r>
           <rPr>
@@ -5378,7 +5446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{9524A10F-3B35-4B50-9361-07DEAF9EC66F}">
+    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{7D8578B9-425B-43DC-B215-7EF10F08E80C}">
       <text>
         <r>
           <rPr>
@@ -5393,7 +5461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00995C78-B5BF-45A5-8F02-B4D6CB8053C5}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{309E82E0-67AD-454E-9A05-4D9313B66A93}">
       <text>
         <r>
           <rPr>
@@ -5408,7 +5476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B614B807-4445-457C-8B76-0D078F087764}">
+    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B9EF8017-E5A0-4B1E-9AF7-1E695ECA49AB}">
       <text>
         <r>
           <rPr>
@@ -5423,7 +5491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{4A9ECB14-4CB2-41BF-A402-F7A28029EC10}">
+    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{26E77479-1563-4266-B2C1-17AF174C9575}">
       <text>
         <r>
           <rPr>
@@ -5438,7 +5506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{B642BE55-802D-4C94-B750-1AEA253BACA7}">
+    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{09D666FE-E28F-48AE-ADF8-2D96C595DB94}">
       <text>
         <r>
           <rPr>
@@ -5452,7 +5520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{CE9B9D72-3B1C-4412-9D79-6D0874D60CEE}">
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{B9267817-21CE-42E6-A675-E3EF4A926E99}">
       <text>
         <r>
           <rPr>
@@ -5466,7 +5534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{AB5427B8-7880-46F7-8737-0E11C545B3E1}">
+    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{D5F41D35-9589-4734-9273-1246C82D90D3}">
       <text>
         <r>
           <rPr>
@@ -5480,7 +5548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{7DADC3D7-B312-4F80-917D-FD030194B70F}">
+    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{68C36586-6425-44D5-AE71-7B83AC0B0D80}">
       <text>
         <r>
           <rPr>
@@ -5494,7 +5562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{E932DAA3-B84B-48A0-A350-BB68775D7800}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{EAF8C373-AE13-4606-898A-ED625C16452F}">
       <text>
         <r>
           <rPr>
@@ -5508,7 +5576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{75AFBBA3-C0BF-47C9-96C1-E2BCE0A5518C}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{A99AB4B1-F894-4133-B7CD-69537AC87FC8}">
       <text>
         <r>
           <rPr>
@@ -5522,7 +5590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{44B4DAC8-1128-45E5-B99C-C84974BBEE0A}">
+    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{66812343-2E7C-44E8-B27C-8CF88CE05138}">
       <text>
         <r>
           <rPr>
@@ -5536,7 +5604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{BFC250B8-BAEB-445C-954D-7BE97AABDFDB}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{384DF3D1-4AA8-4943-A530-5AAE715E42E7}">
       <text>
         <r>
           <rPr>
@@ -5550,7 +5618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{AEC7DAF2-9B1C-4CBB-B735-E9AB7A0CFD03}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{1DE26347-7149-43FD-858E-465A040CC0F3}">
       <text>
         <r>
           <rPr>
@@ -5564,7 +5632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{5757C298-3224-4FCB-AE44-57AE2804657A}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{B687D13E-D130-42E7-9D6A-3F80F0C7EF5D}">
       <text>
         <r>
           <rPr>
@@ -5578,7 +5646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{32018E11-B6CC-4CB9-AD83-CDEAB15CB02F}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{9BC31D67-F810-46D7-B5A1-4288AAC1F5B6}">
       <text>
         <r>
           <rPr>
@@ -5592,7 +5660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{548CA939-8049-4A22-8DCF-97B43275D455}">
+    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{64D245B3-8DA5-40BE-BC14-2456737D9F8E}">
       <text>
         <r>
           <rPr>
@@ -5606,7 +5674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{B79D2BBE-1689-4CA2-9F3C-27F21A096995}">
+    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{5798986F-DE4D-469D-8D38-C4A254954155}">
       <text>
         <r>
           <rPr>
@@ -5620,7 +5688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{521B8842-9FA3-4AE6-9999-7E38BD5734E2}">
+    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{1683DE01-9F25-40E0-AE29-344104540630}">
       <text>
         <r>
           <rPr>
@@ -5634,7 +5702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{745C521C-CEC3-4590-B658-F244E03502B3}">
+    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{6E399964-9FF6-4F4D-B47E-AC805C54B9BA}">
       <text>
         <r>
           <rPr>
@@ -5648,7 +5716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{48501DF5-33AD-4137-BF61-A1ACEF3712BB}">
+    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{EFF89D0F-5E10-4447-B0BA-64F660AD6D14}">
       <text>
         <r>
           <rPr>
@@ -5662,7 +5730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{52DA180B-0E50-41F0-B433-76D057FD32AA}">
+    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{E024415B-2F81-4A00-9886-75203AC76837}">
       <text>
         <r>
           <rPr>
@@ -5676,7 +5744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{1827DF80-3E7F-4FAE-B545-321A48A20B7F}">
+    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{773BC8B9-C7FD-4E1D-BFAD-28167A2B0241}">
       <text>
         <r>
           <rPr>
@@ -5690,7 +5758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{428ADF28-94CB-45A6-B512-653753D79D4A}">
+    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{E0893EE6-8215-43BF-B8DC-C2BA125EF501}">
       <text>
         <r>
           <rPr>
@@ -5704,7 +5772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{E327363C-87BF-426D-8031-8E5B15B868F6}">
+    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{B0106407-B25E-404E-AE98-C6E846DE7439}">
       <text>
         <r>
           <rPr>
@@ -5719,7 +5787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{0FC0F10D-E16C-4929-8C9C-BBCE7D585B2C}">
+    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{B3781CC1-6735-4678-95E3-B6650A0CF979}">
       <text>
         <r>
           <rPr>
@@ -5734,7 +5802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{83AA2241-D1A0-473B-BB01-4502DE008F6C}">
+    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{550CF970-1632-472E-99A6-5157A6C70FB5}">
       <text>
         <r>
           <rPr>
@@ -5749,7 +5817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{AB840D19-E9DC-41E5-8B1A-28772D27BB6F}">
+    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{0F529DF4-B0D9-4A77-880D-52378457049B}">
       <text>
         <r>
           <rPr>
@@ -5764,7 +5832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{28DA7237-5B4A-4888-B612-1517D8E4181A}">
+    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{0A749486-D0DA-44DD-A158-4937B013D9E1}">
       <text>
         <r>
           <rPr>
@@ -5779,7 +5847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{24B15358-0318-4650-A1D9-ACBF45D6BD86}">
+    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{65A87F96-9920-4AFF-9D42-432A9BC46A37}">
       <text>
         <r>
           <rPr>
@@ -5794,7 +5862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{3CCBD856-2028-4562-873C-EF798B7CEB0E}">
+    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{14AFEBEB-6E6D-485B-AD84-D77832449F6B}">
       <text>
         <r>
           <rPr>
@@ -5809,7 +5877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{515C103F-DDC3-40D5-AA24-3704C957FBDF}">
+    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{C956521D-520C-46E0-BBF9-22BA4AB5823B}">
       <text>
         <r>
           <rPr>
@@ -5824,7 +5892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{2B07245A-D9DE-402F-8C94-59F9204780AD}">
+    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{889435D0-F1CE-49D5-B3FA-2C346C3DD8BB}">
       <text>
         <r>
           <rPr>
@@ -5839,7 +5907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{B09F6ACE-9930-4B23-AC49-D976E3AF6D20}">
+    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{21DCB560-D7D0-454D-9256-2EB6BA5D9FAF}">
       <text>
         <r>
           <rPr>
@@ -5854,7 +5922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{08D07A70-B0BF-4318-BF4F-F0DBC6170F84}">
+    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{2CA48B3A-F458-496E-A12E-9EDFF9710F14}">
       <text>
         <r>
           <rPr>
@@ -5868,7 +5936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{76EC0005-9898-4CC7-A802-EC15F25448F0}">
+    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{D5130B5B-6564-4541-AFF7-B31DC2A99F0C}">
       <text>
         <r>
           <rPr>
@@ -5882,7 +5950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{E5FFA232-5153-4095-946B-DFA45A9FBF8C}">
+    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{A87CEC0D-D5EC-411A-9E0A-45792CF26B1E}">
       <text>
         <r>
           <rPr>
@@ -5896,7 +5964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{AFCCFA07-E0EB-45D3-B7C0-514815792647}">
+    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{F07A7990-2D7C-41E0-8069-25EED27A8B7D}">
       <text>
         <r>
           <rPr>
@@ -5910,7 +5978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{C392BCAD-8C69-4A4C-87EF-377772EECC28}">
+    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{B9A5DC53-F533-4CB3-94F1-5C0DF398AC61}">
       <text>
         <r>
           <rPr>
@@ -5924,7 +5992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{E3317A10-0BE4-48FF-9352-A01B5BA3FEE5}">
+    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{F61BC170-6314-4BE8-BD27-ACBE21EC6D83}">
       <text>
         <r>
           <rPr>
@@ -5939,7 +6007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{67EC6033-7BEB-4400-84EE-0A8533A907FD}">
+    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{F2F9EF38-F3FC-4F8C-BAEA-4602406D7D4B}">
       <text>
         <r>
           <rPr>
@@ -5954,7 +6022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{E94FC89C-5249-427A-BE28-D6BFC2F81758}">
+    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{03156B19-EF6A-4B80-952F-EA4B39906AB2}">
       <text>
         <r>
           <rPr>
@@ -5969,7 +6037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{AA56A34D-E716-48F4-B898-FA37D2EF7D4D}">
+    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{6C70B7FC-07DB-4AA6-AD5D-BA8D185F69A2}">
       <text>
         <r>
           <rPr>
@@ -5984,7 +6052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{90492BA0-E368-47BA-98D1-DF7E39D86EF5}">
+    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{ECCF229F-BC05-441A-A8EC-996A647C989C}">
       <text>
         <r>
           <rPr>
@@ -5999,7 +6067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{9CD81021-C7F5-4F80-9E36-5A372FBC35BF}">
+    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{853363A1-995D-434E-99B9-CBFFCC587E17}">
       <text>
         <r>
           <rPr>
@@ -6015,7 +6083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{49DF1121-32A1-4036-AEE8-BCAAA6147B06}">
+    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{D7049EC9-BADF-40DE-979A-0A74E0293BB1}">
       <text>
         <r>
           <rPr>
@@ -6031,7 +6099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{9499DF21-B57E-420A-A749-CC9BF2D4D725}">
+    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{C916B5A2-27DC-436D-B575-9210A24C214D}">
       <text>
         <r>
           <rPr>
@@ -6047,7 +6115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{4524A951-07DC-487B-A233-43D4EAAEC701}">
+    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{D9F9FF7F-8008-4D79-ABB3-028FF22CD559}">
       <text>
         <r>
           <rPr>
@@ -6063,7 +6131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{889D9E25-29F0-4C18-931F-58D4600ECBE1}">
+    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{D7D5CD6A-B8A4-4771-AAA0-5113E0A3BC1F}">
       <text>
         <r>
           <rPr>
@@ -6079,7 +6147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{678FE956-BF94-4DA4-81E3-20DDE72682D7}">
+    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{06B708C5-CF4C-4BD9-A112-999F5C581700}">
       <text>
         <r>
           <rPr>
@@ -6094,7 +6162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{6CE9DBC0-F411-450C-ADE5-6FE43AB51348}">
+    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{652C7700-A4E9-41DE-B7A6-091614D48006}">
       <text>
         <r>
           <rPr>
@@ -6109,7 +6177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{F2C8AB55-E76F-4187-99C2-69AB2BD9809A}">
+    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{C648195E-E2CA-46F6-BED8-ABE76E4EB10D}">
       <text>
         <r>
           <rPr>
@@ -6124,7 +6192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{D025E63E-9D67-4225-8627-D53B10AA6DB9}">
+    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{876F0647-9D39-464F-9AEF-66CCB9E7BEE5}">
       <text>
         <r>
           <rPr>
@@ -6139,7 +6207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{E220EC8B-3A48-4133-BD12-15E3EB9F00B6}">
+    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{A2FD75B6-2FF3-4112-A257-87C89428A222}">
       <text>
         <r>
           <rPr>
@@ -6154,7 +6222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{74D29CD4-44A4-4706-B0D2-5EBDC4B70B6C}">
+    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{17B0E3BD-602F-47AD-8FDA-505C553A7C4F}">
       <text>
         <r>
           <rPr>
@@ -9917,7 +9985,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tJJskf1M4oaaBbkYVWvc02OUYKNNbavh4wQ3UhAtD6Cx3JfXIvkNeJgoLf28AUfN2seXRmDwncF8vAbswND+BQ==" saltValue="dQfSDuTABRBrwy272mO93Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="mUgki0GeJy3+k8eg9eTM1ZAinRdkTdiN21/JgcL/dfbgdiTEIKsZ9Stpd3dE2wntvO5st1l3QhOUsApziFnwTA==" saltValue="7HF9+N1VMJ+dQ7edfjQTXQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10842,7 +10910,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/ewkRSwpGcbTE0JmugXmX7dWVSg/VEi/sDx40quEkKYO02CjDpxTHAoCoruYKHI35zT9w88O4AVMxqCNRlTbug==" saltValue="tl+eXjOo35Ir3ZNwCF8/YQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QNfa0D5XhM9UUZXWZppD8kYh5mO42ndpDmBB/c6RazqOVXlusgE2MFVHoYHBb4mXOWyiS1kIiOhxOQXP2GVVJQ==" saltValue="iFnJVl/oAau3A5uXvXx+vw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10995,7 +11063,7 @@
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="UkPai+wAl9MTVWXJRfvA2QMsXthlSj81NuM4UTsMUX1A9u+YDRef15Cuh8dT0zJE+7GUjjLY5WX/PX+iNktWGg==" saltValue="0qxTe5fgN3Eo4va+nAPxDQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rFnPnSdHeTBQIdIKzh0pgF0AF0adfhb8Xhs/HHdYc6qZKkgDq+h90+4YNQh/bwebu3Y78Dy3rwag/5VXAns6FQ==" saltValue="C2ScZHbNAnBEsfIDehiswQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -11093,7 +11161,7 @@
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xa55/akKOqylFiUpRPImuFE/criap4UK0ISiRSJSxVKmq0w4Lv88oHW4TJckLBLi6YhOH1IWsnBoMznidvty2g==" saltValue="dIEsvIh/nb1KpYzaYAI7/g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1dyCxqbEcbX8WtFkgPs48f/5PlImbSQ5UYqb5MVyPyzxDy1M85I3ykoOI+pI0kTOECAduj4Mcbn8Pnf3OSLt+A==" saltValue="fUrqvfkY/rVyuf57IKrwUA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -11203,7 +11271,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="X+BwOG8WfmP/B+78Z+i3BXWTj79oLwsP+5iGAYzOERhLgLaoW0cXN8mzXhxxce6VXU9vhf2qVcBvCJfrWJL/Rg==" saltValue="oM/LsGJWok4wImremJ9J8w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LUxBShLY5OpilAxZIMZOZvCAacM8M2BFHoT+GPxX6BfUmsQfu6sEONN69mik4PNdXSgU+k9akRPmusc3lUkgtg==" saltValue="KjxL9sOb3LKjUDSYMbZwdA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12961,7 +13029,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6NtUPnTUS0cYwePEBvWVccpPRt7LuuaZyXKs2Ppyhmrit2qS+ibIsWBb6ZFn3zKkYT6vDG8QXNHEIWbh1QZgAg==" saltValue="Uw8rffhP1sXIhCRF7awxpA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TsTgbFQzUSwEbK60NY/a8669jVXkD2cq98YuPCuYtt6BptKvz/5rLBSAMJ6axthzN5Ph3w6MMaidTKuzlMlcjw==" saltValue="S5jFdFGJkG3PsgUjTE+Xcw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12994,7 +13062,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="u2h+5bxkonrjCLTywfv7Oa4TP/RAP7WPmSFqk9N2iFFo4j6uKzz8tumXnCcLnDMEjBbP4qBgnuZd6fDDuk2DFw==" saltValue="aatupDPZOBud1bap7fRLng==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gbCZdoYaQsrixD1aqni11qd5U40cEfgzs+8CtsTealsC/do55/LmWYf/T3Dkln+JeEWoP/UnctXUoSoba+1LbQ==" saltValue="pYaunjNFhlPd4PhUQOTnaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13195,7 +13263,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3n4PkXsgq2y3XCl8gT4NHQcL2rUL/D2eY/q8+5iO790ThT6mzo+w/OCciTWsGclzK+2ZX7XQtoozJYHz8qxTjA==" saltValue="uWwg8by2g0D0YyZ22OQrYQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5G7MLHalawB4hK2W5WSSYD+IVKGh/Uq32N0DFTZunZ4PRR3RHBIi1sLTqY2bfgJwT3U9vFN4y2GZ65j5btvL8w==" saltValue="GkdC5UnMfQ5iZeYpo7onjw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -15005,7 +15073,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GQJ6sCxFOxgTYlnUSlP2rwKHsDWTz40ArqklhIgtkd7HKs4i32Sw3dJ0JUQ4ZruQ1d2KIG2Fm5MJ56aDBJSdsg==" saltValue="IToj8YjAASe3RVzy89wARA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ozDBg75fr7H3F5aPY45i3tNoGFj40vOLKI9L3uPOfdz/w8RdMBULF/UTBGZ7hGFP9lqudy0cPGGci/iI5cnjQw==" saltValue="Odx7IZWOP1aTQHNfHLPc3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15816,7 +15884,7 @@
       <c r="L39" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IcVnnaJI4EpmLZi71HEDmnD8dqKpVqHu5oTD5e0NWUelAHhacpoJAwdzn3FtYDspUQhQV05KB3hr64tBrgmBxQ==" saltValue="syk+LJq86GgR2CSiOY0o+g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GPo+vdZ0tSVbgeDoSj+hrNasJ+L9Hg7HdbclVs4RjOxSMhTAg8J3ta95uUmnoEJsanfBggu5PezuccZlMpkG4g==" saltValue="+SJ4t3EtuyCtjRp8jcFTog==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16209,7 +16277,7 @@
       <c r="L14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="A9z/ChNrD7AT3cOOO93wbwV5vdS33S/4P4AO2mIhVpDTjyED/7zbbCHd2Bv9Da6pfolxrFNv4qfl8pWbRoHjRA==" saltValue="2mxDs9cEI2kPZmJeNopxBw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BSmsPnSfqIl66kwF4oR6oMBSymH6+RatnfqSQKsPKGG1BQu2MfjbMzD/vxONpCsF8yk9nizmqdLquyJYAjXA0Q==" saltValue="GdyRLXbBqweBs7YTXGocww==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17058,7 +17126,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JGUIbu//JI86UHJ2QpiaIeKUBld7ILwcwJOwiXudqaoo8ycMAybLF6F6frcnDIpjeTCUDb4JFGbmeThQXYny1A==" saltValue="ucBZriK8c3geeyIRCy/dZQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9F8mcj62H75Xa7ewMtGfQ/lqYpaxudXvRYZLai2J5lQcQ4z8l5Kqmja72u3Z1Dl4zz5zaneJxSFdyTejRigJoQ==" saltValue="JS9G4fT6/C4mlnEhm2v/aA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -20855,21 +20923,24 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Y7qDylQxWThjlJcglhhxQ2TrtW/ZiwMFKiekRsDTG2z6VOL+xheJVQY+/VSOsRsvOAGnce0H5HjECaDgnOaRtQ==" saltValue="ZmeMvzcXicwspqKS+qopQg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="p9joqDFqnCZ1nujvCYvbHC/iKRxBB1yBknZ0KkvmXK52QqRRYhaK6C5AXplPHXBggugLeSpqeYzoC5r5MM7ZuA==" saltValue="TJ/ywlz/EneXviWrK4sp+g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B28:B30"/>
     <mergeCell ref="B154:B156"/>
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="B95:B97"/>
@@ -20886,22 +20957,19 @@
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B128:B130"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B89:B91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22002,7 +22070,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7AC7b5J0d0oF/yuV4y9qOCFJVY+RgiEHBd46qLaWNuUFrbw7yzdeTJQpFqDuYfiFEWIn6DllcfzJvH7PSBhV9w==" saltValue="Zi7y/O1NDBA4nH1c0BtXUA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YpvVRR0czl2VkjLtRN90SZCdjs/7s7oYmQiYF6r2iP37GwdH4Ar7byVkv7skB8zZiwLYS7QUswi9d15SIHnSEw==" saltValue="ePu/Rt9dpMwIjTeH48aOxA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -22943,7 +23011,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pyYMkU/iBaei+As5PI9McUhK8JCDvZDjTJIaJ3N9g+SCzbLQ+k48+gTDGxaJlcxcMAABx2lvgu1wQJ1aVtGiKg==" saltValue="DsWZccpwrhIpSqJDy1Tfsw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KO4BPoN08LTgaeoAfxjei1aPMT7SoAulZemnV1wkKrB9HXVFH8EqQS8PMqPGTftK84rGV5i4eARO/exRYT0ZTQ==" saltValue="e2UAqI5O3r20pVr4ydsZLQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -24159,7 +24227,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7wOYPDBd4ZrQVsUhbTJmgs/US5pBNga5uAsEe6in2fTSXVq04GFO4q4cfOFMqg4FCN0RHI3FNy3oIfTZHpjjPw==" saltValue="G73+BD0u6yWtwI4OpjqcTA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="b/ZPodb391baqayAE8nMO/h87j2gg24dffuHRalIk2yggTbBYcweeL/Ugr2R7DtRtg3TW9yMabqflHPWm5Ngyw==" saltValue="CyPwfJ3pxyI6GdD5xqhYNg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -32294,7 +32362,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9yNE8Osz92SglPfXc1CLuGmcxXcSA2YVfM6ROY15hHADfMs9EDkSvor1D8XfUA4CLUWtmV3+AwcUwLs7T7VTOA==" saltValue="WOdsIDGW01v0wggpsj0AEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kQ0ahocGiAXN6zjk17yVWI6Jh63zFun/2vnznQZXYLZaX6yRMlxzKI8lQPyxi0nK/v+So0ortlXiOfUZO3PJJg==" saltValue="Iyv5+1EtvWB85QMyKrj0OA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -33588,16 +33656,16 @@
         <v>1</v>
       </c>
       <c r="L33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="M33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="N33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="O33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -33795,16 +33863,20 @@
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <v>1</v>
+        <f>L31</f>
+        <v>0.38</v>
       </c>
       <c r="M37" s="90">
-        <v>1</v>
+        <f>M31</f>
+        <v>0.38</v>
       </c>
       <c r="N37" s="90">
-        <v>1</v>
+        <f>N31</f>
+        <v>0.38</v>
       </c>
       <c r="O37" s="90">
-        <v>1</v>
+        <f>O31</f>
+        <v>0.38</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -34726,16 +34798,20 @@
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <v>1</v>
+        <f>L54</f>
+        <v>0.7</v>
       </c>
       <c r="M60" s="90">
-        <v>1</v>
+        <f t="shared" ref="M60:O60" si="16">M54</f>
+        <v>0.7</v>
       </c>
       <c r="N60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
       <c r="O60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34757,39 +34833,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="16">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="17">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34804,11 +34880,11 @@
         <v>200</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:D67" si="17">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D67" si="18">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
@@ -34850,11 +34926,11 @@
         <v>201</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
@@ -34896,11 +34972,11 @@
         <v>202</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
@@ -34942,11 +35018,11 @@
         <v>210</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
@@ -34984,7 +35060,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="N9iJRgaFEj/+ua+5AE/mCqUdoX/Kx5YGLZd80WsIsazRY8OpVD+caaVlT6BGRgnfM57RqhDhuK7J8uWq7o/xYw==" saltValue="6UOEbVu7nB4k+lm7IPGGiQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rzKd0pemSuwQm/qVl1XdP+Sgj4ZScn49Xo9JqZeo88tLo+ZcSD46xllP3IVNM4iWl1E1wUMuZCHn8wzTpdrjcg==" saltValue="7qWJdVoztkL+24mdRKf9bg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -35266,7 +35342,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/OX8YcTCIfL0oXlnvj7hlj9VI7MxCfg7LAhSXrBv9CMShwgUJigZALjL++0ABvoapSeKDae0gAobvc7h9HhyEA==" saltValue="w5ZE1xUOfXsb3Xc2sXrwqA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="qa5L0sF8mjhKJ/WxRXMGaM7IbNN3PAUDBma+HghP4EQ1MQg1XRJN8+uI0wRyCSy/bbHHZlg7D5RhRmLgLRv1Hw==" saltValue="3UsdSlVCWxcvtZgQYFKtAg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -39126,7 +39202,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="y8VVOE/w8nT54Uq5J7LuLaPInvosujyOoc3a8O72Xk0NTj5ZVKSbxNaxaX6EXJNr2KsUiZYK9E6zcMfLOI9oCQ==" saltValue="3HdL8ru8TDZrj+2t1lCAKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="x3UYdRYx4+XiAtjrskgYsw5PoL7gCOECInDt7qZu6VuA5793vqqimE1dB9I42gxckdlMziJBx13a7i7jUdyCRA==" saltValue="T0S+J3c5I1VKbeLyZgXZrw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39766,7 +39842,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="E25IySk+wt6e18x3kuMz3ut5DTCeEqYn5wYLNPCC1w0TzhDtO8Z1zDyv672NvS27czL0yr5Rvi0ek/S3GDuMzg==" saltValue="Q6Icm2/2HfdXphTYwDHoxg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vdF3qruPlaflq/GDCVtAhsdFGNRrXT96tE2OCSqkbZ0+EbXmRVM6bwHmlPPYKdnQVzLTLqMs9mvmfZzfP5WrAg==" saltValue="3yrF+EsuX/UkvzGkG0sb3w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40199,7 +40275,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qK0h7dbwFf4LPzzY+Z6YxZwayFbp2UlWjyc7KWvH3LfADMRWvQv+btMdQE0j1cxt7+yOdxEN5hJpNFTPYN3vpg==" saltValue="tkDAn4gEEVUPD45zUki+ZQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/8O8A48sq0RE5L28+Kh5tcc3t3Q/E2opiI8zR9krnZSvgPbyeuqmFnun/L3rvFi2OjWcLzd3KoahAsHrdYweTQ==" saltValue="ZPWKoDPN80E5CDWheVImXg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40618,7 +40694,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rbYSgDzgf4SLqQwC5rSWX4EcwOUPdiCootQXDg1A183eopRymStjiKmsVD49Q1kKLZ5ISjKQeJcD8VLYAwmWRA==" saltValue="4qT26rUwT51OKi8PV117Ig==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="G8Q/lv2HasTNcXLwdX3IsPE95eF5Camn11GE7DUV45pm4j5UKfWevG+mF64EN6hpey8u9ggbyrORL7uuxOKMCg==" saltValue="R4uBA8FAAs/1+CX0wtSZfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40750,7 +40826,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="aT/KcceCnsZ6xcuz3xnqUH24J5reP9+sL7G5MflGegnzWo0M1cMoBo47AJamJ/2UFj3J7TGuuVNP2G1zVIZ4sw==" saltValue="oGVJo4TY2XXYVprgsw6Qrg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0S0qrD4X+hPMAAEpczkms7ZDbiX8+6jQH8fJCKJJeNPx8fAVBTrR1aHSNTwE+i4TQF7aN8bU8z7bTV6aC4T78A==" saltValue="IOTfbtQ9Y27PUyLSX8GGhQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40951,7 +41027,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="j3wJwU0W/RVtTH9qloWBP5M8oXq58Mg1EaIgv0GXT408du+V+qeBZGAShVuChWKevWxouhcaXRWKNplBMC8hKg==" saltValue="sT2gq3A/ym+FbAabU4clSA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8Qf/mmR40Yy89muAemF1wuLEKXbUm12B7KWR8s6h+avNY7hieqRjBq/nhrukl198TXQgXlvS94BQ5ql78MvxTA==" saltValue="ucvcmIbngpliDVRX0+u15g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -41476,7 +41552,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="w4iYM9+9gP61300gKMkHTxBFlySOc7eQJIHa5kVyX1XmooF2n1CuEpB4GuRn4hDm4Ljfgf0NBcaOvyW2HNJOLQ==" saltValue="1J9/GN4GvqhOWnKav0327g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ViQnKUOsvrOVF4TVFAPZbsUxkJCwlUsMaAHt+C+4eo029tn4z8odTu9MjEMw2BwkDTWGiob2ysrJgCtZVrHQ4g==" saltValue="yzereKvfU09fLS+ZL8iqWQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -41735,7 +41811,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jM8ljsid1dyllZpZOkfQ0GnLYc3/Q2EEIX1crmGU/5DO37pIq085klD4G5C5O70NMv0RP+h0ZKVurG9C+Mc9XQ==" saltValue="FQQyD8p6+DQUJsLPfob4qA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1KM4tP4lWzZY2hkndO4+QYOLuUxlETvYeIAgQH33VP/QBCUQlbO9b/oGl5xtd2z6C2562UzRa76WJv7OnAlSAw==" saltValue="04R6vq9EzA2WrYrwwMpxcg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -41794,7 +41870,7 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1+zIi4AytVebAnnkccb2r6BHWV3p7cgD2kSRVxKaip8CgwTNKSq9/kiDsyiy6/Rbcvs9gOYFAc9ZKQ9PNo+hzQ==" saltValue="xA0ONEamsekCVTG92fnn/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="n+jlPlDneT5kc9DQDobRLEcPQThdJ/r/C1+Xc5iQy1CasiveGKz5OH9gWN2m+7BP9jXi8MdqqJW6/XIpwVhB/w==" saltValue="IMldUVF8M5bevEuav9LG/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -41810,17 +41886,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f77cb9dc30d15950233dec29875e7d3d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7972fb108f377c3e0c6a81e726e76be" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57ec1f31440e439775915f75cb7954ca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="62245b0892ab2a20b5f44f74e1fbf663" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -42002,6 +42069,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
   <ds:schemaRefs>
@@ -42013,15 +42089,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AE9A51-FA73-431C-A4D5-36C1DFA1FEFD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB7E161-F495-494F-94F7-37757C779909}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -42036,4 +42104,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>